--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461142.5293133074</v>
+        <v>461143</v>
       </c>
       <c r="R2" t="n">
-        <v>6296814.851568805</v>
+        <v>6296815</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461142.5293133074</v>
+        <v>461143</v>
       </c>
       <c r="R3" t="n">
-        <v>6296814.851568805</v>
+        <v>6296815</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74269619</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253879</v>
       </c>
       <c r="B3" t="n">
-        <v>99336</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25812-2025 artfynd.xlsx
+++ b/artfynd/A 25812-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74269619</v>
+        <v>74253879</v>
       </c>
       <c r="B2" t="n">
-        <v>99422</v>
+        <v>99802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4E9c 4419. SOM: Carex pulicaris. LEG: Åke Widgren</t>
+          <t>Smålands flora 2007: KOO: 4E9c 4419. SOM: Carex hostiana. LEG: Åke Widgren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74253879</v>
+        <v>74269619</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222322</v>
+        <v>222361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4E9c 4419. SOM: Carex hostiana. LEG: Åke Widgren</t>
+          <t>Smålands flora 2007: KOO: 4E9c 4419. SOM: Carex pulicaris. LEG: Åke Widgren</t>
         </is>
       </c>
       <c r="AD3" t="b">
